--- a/practice/answers/q030.xlsx
+++ b/practice/answers/q030.xlsx
@@ -12820,14 +12820,14 @@
         <v/>
       </c>
     </row>
-    <row r="5" ht="46" customHeight="1">
+    <row r="5" ht="64" customHeight="1">
       <c r="A5" s="5" t="inlineStr">
         <is>
           <t>(b) The part b lookup returns the #N/A error -- there is no ALONSA row for SY Manness in 2023.</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="46" customHeight="1">
+    <row r="6" ht="64" customHeight="1">
       <c r="A6" s="6" t="inlineStr">
         <is>
           <t>(d) A missing combination means the data holds no result for that variety in that municipality; a zero would mean it was grown and produced nothing. Treating absence as zero would invent a catastrophic yield that never happened, so the two must be kept distinct -- which is what the if_not_found message does.</t>
